--- a/input/ES/alignment_targets_partnered_share.xlsx
+++ b/input/ES/alignment_targets_partnered_share.xlsx
@@ -91,7 +91,7 @@
     <t>Produced</t>
   </si>
   <si>
-    <t>11 Aug 2026</t>
+    <t>26 Sep 2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +545,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="14">
-        <v>0.60143226385116577</v>
+        <v>0.60160195827484131</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +553,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="15">
-        <v>0.60615402460098267</v>
+        <v>0.6063578724861145</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="16">
-        <v>0.61146295070648193</v>
+        <v>0.61176770925521851</v>
       </c>
     </row>
     <row r="5">
@@ -569,7 +569,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="17">
-        <v>0.61138659715652466</v>
+        <v>0.61140424013137817</v>
       </c>
     </row>
     <row r="6">
@@ -577,7 +577,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="18">
-        <v>0.60501253604888916</v>
+        <v>0.60505896806716919</v>
       </c>
     </row>
     <row r="7">
@@ -585,7 +585,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="19">
-        <v>0.59829884767532349</v>
+        <v>0.59831339120864868</v>
       </c>
     </row>
     <row r="8">
@@ -593,7 +593,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="20">
-        <v>0.59542906284332275</v>
+        <v>0.59545344114303589</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="21">
-        <v>0.59341025352478027</v>
+        <v>0.5934106707572937</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="22">
-        <v>0.58612287044525146</v>
+        <v>0.58612328767776489</v>
       </c>
     </row>
     <row r="11">
@@ -617,7 +617,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="23">
-        <v>0.56142276525497437</v>
+        <v>0.56142342090606689</v>
       </c>
     </row>
     <row r="12">
@@ -625,7 +625,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="24">
-        <v>0.57639038562774658</v>
+        <v>0.57639050483703613</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="25">
-        <v>0.5832362174987793</v>
+        <v>0.58323633670806885</v>
       </c>
     </row>
     <row r="14">
@@ -641,7 +641,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="26">
-        <v>0.57984286546707153</v>
+        <v>0.57984322309494019</v>
       </c>
     </row>
   </sheetData>
